--- a/docs/triton-learning/cards/triton-lesson-01-vector-add-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-01-vector-add-correction.xlsx
@@ -41,17 +41,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">masked load 的形状由什么决定？</t>
+          <t xml:space="preserve">Triton 向量 kernel 用一组局部指针执行 tl.load，并用 mask 屏蔽尾块越界位置。返回 tensor 的 shape 由什么决定，false 位置会消失吗？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 · L01 知识复述中的真实纠错</t>
+          <t xml:space="preserve">Triton 3.7.1；每个 program 用 offsets 生成一组元素地址，尾块只有部分地址有效。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">由当前 program 的局部 pointer tensor 形状决定。</t>
+          <t xml:space="preserve">返回 shape 跟随该 program 的局部 pointer tensor；mask 为 false 的逻辑位置仍然保留。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -61,26 +61,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：mask 不会把 false lane 从局部 tensor 删除。
-• [T#B#例子]：四个 pointer 配合 \[T,T,F,F\]，load 结果仍有四个逻辑位置。
-[T#B,!c47f17#边界]：不是整个 PyTorch 输入的 shape，也不是 wrapper 分配的输出大小。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：tl.load 逐位置处理传入的指针，因此返回值具有这组局部指针的形状；mask 只控制各位置是否读取内存。
+• [T#B#局部形状]：例如 offsets 有 4 个位置，x_ptr + offsets 就有 4 个指针。即使 mask 为 \[True, True, False, False\]，load 结果仍有 4 个位置，而不会缩成 2 个。
+• [T#B#无效位置]：false 位置不从对应地址读数据；指定 other 时得到该替代值，未指定时不能假设其数值有效。
+[T#B,!c47f17#边界]：整个 PyTorch 输入有多少元素、wrapper 为输出分配多大空间，都不是这次局部 load 的 shape 来源。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">条件 store 怎样避免越界？</t>
+          <t xml:space="preserve">Triton 尾块只对满足数值条件的元素写回，例如只保存大于阈值的结果。tl.store 的 mask 应怎样组合，才能保证越界地址永远不被写入？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1 · L01 对 sentinel 的真实误解</t>
+          <t xml:space="preserve">Triton 3.7.1；offsets 可能越过长度 N，boundary_mask 表示 offsets &lt; N，condition 表示数值满足写回要求。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">显式使用 boundary_mask &amp; condition 作为写回条件。</t>
+          <t xml:space="preserve">使用 boundary_mask &amp; condition；地址有效和数值符合条件必须同时成立。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -90,9 +91,10 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：边界安全由地址范围谓词保证。
-• [T#B#失效原因]：某个填充值可能恰好不满足当前条件，却在阈值或比较条件改变后通过。
-[T#B,!c47f17#边界]：不能把越界安全寄托于 sentinel 的数值效果。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：是否允许访问地址，应由边界条件直接决定；是否需要保存该值，再由业务条件决定。两者取逻辑与，才是完整的写回条件。
+• [T#B#填充值的局限]：例如 load 对无效位置填负无穷，它可能刚好通不过“大于阈值”的判断。但若以后改为“小于阈值”，无效位置就可能通过条件。
+• [T#B#稳定的保护]：即使填充值通过了 condition，boundary_mask 在越界位置仍为 false，因此最终 store 不会访问非法地址。
+[T#B,!c47f17#边界]：other 是未读取位置的替代数值，不是 tl.store 自动继承的边界保护；不能靠某个特殊数值恰好被过滤来保证安全。</t>
         </is>
       </c>
     </row>

--- a/docs/triton-learning/cards/triton-lesson-01-vector-add-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-01-vector-add-correction.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -41,60 +41,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 向量 kernel 用一组局部指针执行 tl.load，并用 mask 屏蔽尾块越界位置。返回 tensor 的 shape 由什么决定，false 位置会消失吗？</t>
+          <t xml:space="preserve">Triton 向量 kernel 的尾块只有部分位置有效时，每个 program 执行的 tl.load(x_ptr + offsets, mask=mask) 返回的 tensor 的 shape 由什么决定？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton 3.7.1；每个 program 用 offsets 生成一组元素地址，尾块只有部分地址有效。</t>
+          <t xml:space="preserve">Triton 3.7.1；offsets = pid * BLOCK_SIZE + tl.arange(0, BLOCK_SIZE)，mask = offsets &lt; N，输入 x 共有 N 个元素；wrapper 事先用 torch.empty_like(x) 分配了与输入同样大小的输出。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">返回 shape 跟随该 program 的局部 pointer tensor；mask 为 false 的逻辑位置仍然保留。</t>
+          <t xml:space="preserve">由当前 program 的局部 pointer tensor x_ptr + offsets 的形状决定，即 \[BLOCK_SIZE\]；与 N、输出分配的大小和有效元素个数都无关。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">根据输入tensor的形状决定的</t>
+          <t xml:space="preserve">“数据目的地已经开辟好了与数据源大小一样的空间，所以返回形状与数据源固定一样”；后来又说“根据输入tensor的形状决定的”</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：tl.load 逐位置处理传入的指针，因此返回值具有这组局部指针的形状；mask 只控制各位置是否读取内存。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：两句都把形状来源放在了这次 load 之外：先归因于输出的预先分配，后归因于整个输入 tensor。tl.load 逐位置处理传入的指针，返回值就具有这组局部指针的形状；mask 只控制各位置是否读取内存。
 • [T#B#局部形状]：例如 offsets 有 4 个位置，x_ptr + offsets 就有 4 个指针。即使 mask 为 \[True, True, False, False\]，load 结果仍有 4 个位置，而不会缩成 2 个。
 • [T#B#无效位置]：false 位置不从对应地址读数据；指定 other 时得到该替代值，未指定时不能假设其数值有效。
-[T#B,!c47f17#边界]：整个 PyTorch 输入有多少元素、wrapper 为输出分配多大空间，都不是这次局部 load 的 shape 来源。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Triton 尾块只对满足数值条件的元素写回，例如只保存大于阈值的结果。tl.store 的 mask 应怎样组合，才能保证越界地址永远不被写入？</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Triton 3.7.1；offsets 可能越过长度 N，boundary_mask 表示 offsets &lt; N，condition 表示数值满足写回要求。</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">使用 boundary_mask &amp; condition；地址有效和数值符合条件必须同时成立。</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">如果写的mask没有考虑边界，就必须要让other=-inf了</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：是否允许访问地址，应由边界条件直接决定；是否需要保存该值，再由业务条件决定。两者取逻辑与，才是完整的写回条件。
-• [T#B#填充值的局限]：例如 load 对无效位置填负无穷，它可能刚好通不过“大于阈值”的判断。但若以后改为“小于阈值”，无效位置就可能通过条件。
-• [T#B#稳定的保护]：即使填充值通过了 condition，boundary_mask 在越界位置仍为 false，因此最终 store 不会访问非法地址。
-[T#B,!c47f17#边界]：other 是未读取位置的替代数值，不是 tl.store 自动继承的边界保护；不能靠某个特殊数值恰好被过滤来保证安全。</t>
+[T#B,!c47f17#边界]：输出预先分配多大、整个 PyTorch 输入有多少元素，都不决定这次局部 load 的 shape；预先分配输出只是为了让后续 store 有地方写。</t>
         </is>
       </c>
     </row>
